--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2c3c4367d755418e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Recaf1da0dda14e85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rf00115093da74d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rfa0eb061249d4044"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R6e182d84944b400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Ref6ab891e5ea4c42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R7d8cedd712e44e6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R9286438a93664e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Radc812bfc3e44e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R6321b943eec04c09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -990,19 +990,19 @@
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="13" t="str">
-        <x:v>规则变化运行</x:v>
+        <x:v>隐私策略</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>session_gap_seconds为1800时的session_count</x:v>
+        <x:v>session_gap_seconds</x:v>
       </x:c>
       <x:c r="C13" s="20" t="n">
-        <x:v>5</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
-        <x:v>项</x:v>
+        <x:v>秒</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>无容差；重新切分会话</x:v>
+        <x:v>无容差；privacy_policy.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1090,10 +1090,10 @@
         <x:v>附加文件</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>可以增加README、测试或运行日志</x:v>
+        <x:v>可以增加README、运维说明或运行日志</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>附加文件不能替代规定交付物或夹带输入、凭据和预生成答案</x:v>
+        <x:v>附加文件不能替代规定交付物或夹带输入、凭据和预生成报表</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
